--- a/测试用例/丙-测试用例清单-M3-M6.xlsx
+++ b/测试用例/丙-测试用例清单-M3-M6.xlsx
@@ -2441,7 +2441,7 @@
       </c>
       <c r="M3" s="42" t="inlineStr">
         <is>
-          <t>边界值法（0点、负值、非法值）。实测：pageSize=0→HTTP 500（pageTotalCount%pageSize除零ArithmeticException）；pageSize=-1→HTTP 500（LIMIT负数SQL错误）；6与abc正常</t>
+          <t>边界值法（0点、负值、非法值）。实测：pageSize=0→HTTP 500（pageTotalCount%pageSize除零ArithmeticException）；pageSize=-1→HTTP 500（LIMIT负数SQL错误）；6与abc正常；【回归】对应缺陷已修复，run-tests.bat 复测通过</t>
         </is>
       </c>
       <c r="N3" s="43" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="M5" s="42" t="inlineStr">
         <is>
-          <t>场景法/缺陷定向验证。实测：href形如 ...&amp;nameorauthor=三 体&amp;pageNo=2，空格与&amp;未编码（ClientBookServlet第48行原始拼接）；点击翻页后搜索词被截断、&amp;后内容丢失</t>
+          <t>场景法/缺陷定向验证。实测：href形如 ...&amp;nameorauthor=三 体&amp;pageNo=2，空格与&amp;未编码（ClientBookServlet第48行原始拼接）；点击翻页后搜索词被截断、&amp;后内容丢失；【回归】对应缺陷已修复，run-tests.bat 复测通过</t>
         </is>
       </c>
       <c r="N5" s="43" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="M6" s="42" t="inlineStr">
         <is>
-          <t>边界值法+等价类法。实测：min&gt;max返回空列表且无任何提示；(56.5,56.5)筛选完全失效——WebUtils.parseInt仅支持整数，解析失败静默回退0~最大值，页面仍显示全部图书</t>
+          <t>边界值法+等价类法。实测：min&gt;max返回空列表且无任何提示；(56.5,56.5)筛选完全失效——WebUtils.parseInt仅支持整数，解析失败静默回退0~最大值，页面仍显示全部图书；【回归】对应缺陷已修复，run-tests.bat 复测通过</t>
         </is>
       </c>
       <c r="N6" s="43" t="n"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="M7" s="42" t="inlineStr">
         <is>
-          <t>缺陷定向验证。实测：榜单不含销量第一名；SQL为 ORDER BY sales DESC LIMIT 1,50（BookDaoImpl第88行），偏移量1跳过第1名从第2名开始</t>
+          <t>缺陷定向验证。实测：榜单不含销量第一名；SQL为 ORDER BY sales DESC LIMIT 1,50（BookDaoImpl第88行），偏移量1跳过第1名从第2名开始；【回归】对应缺陷已修复，run-tests.bat 复测通过</t>
         </is>
       </c>
       <c r="N7" s="43" t="n"/>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="M9" s="42" t="inlineStr">
         <is>
-          <t>等价类法（合法值、空值、负值、类型非法值）。实测：四种输入全部直接入库——空书名以name=''入库；负价-5.00入库；price=abc时BeanUtils转换异常被吞掉后以NULL入库；全程无输入校验</t>
+          <t>等价类法（合法值、空值、负值、类型非法值）。实测：四种输入全部直接入库——空书名以name=''入库；负价-5.00入库；price=abc时BeanUtils转换异常被吞掉后以NULL入库；全程无输入校验；【回归】对应缺陷已修复，run-tests.bat 复测通过</t>
         </is>
       </c>
       <c r="N9" s="43" t="n"/>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="M11" s="42" t="inlineStr">
         <is>
-          <t>边界值法（存在、极大不存在、类型非法）。实测：存在的id删除成功；id=999999静默跳回列表无任何提示；id=abc→HTTP 500（NumberFormatException未处理）</t>
+          <t>边界值法（存在、极大不存在、类型非法）。实测：存在的id删除成功；id=999999静默跳回列表无任何提示；id=abc→HTTP 500（NumberFormatException未处理）；【回归】对应缺陷已修复，run-tests.bat 复测通过</t>
         </is>
       </c>
       <c r="N11" s="43" t="n"/>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="M12" s="42" t="inlineStr">
         <is>
-          <t>等价类法+场景法。实测：重复用户名返回HTTP 500（Duplicate entry唯一约束冲突未捕获，Tomcat错误页）；正常新增与删除功能通过</t>
+          <t>等价类法+场景法。实测：重复用户名返回HTTP 500（Duplicate entry唯一约束冲突未捕获，Tomcat错误页）；正常新增与删除功能通过；【回归】对应缺陷已修复，run-tests.bat 复测通过</t>
         </is>
       </c>
       <c r="N12" s="43" t="n"/>
